--- a/质量改进诉求流程表单.xlsx
+++ b/质量改进诉求流程表单.xlsx
@@ -2359,7 +2359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2475,35 +2475,39 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>是否接纳</t>
+          <t>接纳版本</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>闭环方法</t>
+          <t>是否接纳</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
       <c r="F9" s="3" t="n"/>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>不接纳理由（是否接纳为『否』时必填）</t>
+          <t>闭环方法</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr"/>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>计划完成期限</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr"/>
       <c r="F10" s="3" t="n"/>
     </row>
-    <row r="11" ht="24" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>计划完成期限</t>
+          <t>不接纳理由（是否接纳为『否』时必填）</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr"/>
@@ -2536,29 +2540,215 @@
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
     </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>四、分析进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="45">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A22"/>
+    <mergeCell ref="A17"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A20"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A19"/>
+    <mergeCell ref="E22"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E18"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="E21"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="F19"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E23"/>
+    <mergeCell ref="E17"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="E20"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="F21"/>
+    <mergeCell ref="E19"/>
+    <mergeCell ref="F20"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F18"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A18"/>
+    <mergeCell ref="F17"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F23"/>
+    <mergeCell ref="F22"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"问题单闭环,需求闭环"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2572,7 +2762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2717,20 +2907,205 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
     </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>三、进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="41">
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A17"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E16"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A13"/>
+    <mergeCell ref="A19"/>
+    <mergeCell ref="F14"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E18"/>
+    <mergeCell ref="A15"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="F19"/>
+    <mergeCell ref="F16"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E14"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E17"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="F15"/>
+    <mergeCell ref="A16"/>
+    <mergeCell ref="E19"/>
+    <mergeCell ref="E13"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F18"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A18"/>
+    <mergeCell ref="F17"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="E15"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A14"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2742,7 +3117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2887,20 +3262,205 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
     </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>三、进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="41">
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A17"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E16"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A13"/>
+    <mergeCell ref="A19"/>
+    <mergeCell ref="F14"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E18"/>
+    <mergeCell ref="A15"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="F19"/>
+    <mergeCell ref="F16"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E14"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E17"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="F15"/>
+    <mergeCell ref="A16"/>
+    <mergeCell ref="E19"/>
+    <mergeCell ref="E13"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F18"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A18"/>
+    <mergeCell ref="F17"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="E15"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A14"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/质量改进诉求流程表单.xlsx
+++ b/质量改进诉求流程表单.xlsx
@@ -9,14 +9,13 @@
   <sheets>
     <sheet name="0-流程总览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1-提出-质量改进诉求单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1.5-子单台账(中枢)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1.5-改进诉求台账(中枢)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2-评审-评审记录单" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="3-分析-改进项分析单" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="4-1闭环-问题单闭环单" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="4-2闭环-需求闭环单" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5-1-验收-子项验收单" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="5-2-验收-总项验收单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="6-填写约定与编号规则" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5-验收-验收单" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6-填写约定与编号规则" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -166,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -216,9 +215,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -606,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -624,10 +620,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>① 提出(含子项)  ➜  ② 评审(逐项通过→生成子单)  ➜  ③ 改进项分析(接纳→定闭环方法)  ➜  ④ 闭环(问题单/需求)  ➜  ⑤ 验收(子项→总项,通过即完成)</t>
+          <t>① 提出  ➜  ② 评审(通过→指派责任人;不通过→打回提出)  ➜  ③ 改进项分析(接纳→定闭环方法→挂闭环单号;不接纳→打回评审)  ➜  ④ 闭环(问题单/需求)  ➜  ⑤ 验收(谁提出谁验收,通过即完成)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
@@ -639,7 +635,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>④ 闭环含两条并行子流程：问题单闭环（缺陷/故障纠正预防）｜ 需求闭环（新功能/优化开发上线）</t>
+          <t>单链流程（不拆子项）；④ 闭环含两条路径：问题单闭环（缺陷/故障纠正预防）｜ 需求闭环（新功能/优化上线）</t>
         </is>
       </c>
       <c r="B4" s="3" t="n"/>
@@ -651,7 +647,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>单据层级与流转规则</t>
+          <t>流转规则</t>
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
@@ -663,7 +659,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1. 一张【主诉求单】可包含多个改进子项（在提出单的『子项明细表』中逐条列出）。</t>
+          <t>1. 一张【主诉求单】即一项改进措施（不拆子项），整链流转：提出 → 评审 → 改进项分析 → 闭环 → 验收。</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -675,7 +671,7 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2. 【评审】对子项逐项判定 通过/不通过；通过则生成【子单】(QI-YYYY-NNN-XX) 进入分析，不通过则该子项终止。</t>
+          <t>2. 评审完成前，提出单可由提出人编辑修改。</t>
         </is>
       </c>
       <c r="B8" s="3" t="n"/>
@@ -687,7 +683,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>3. 【改进项分析】由分析人决定是否接纳；接纳后决定闭环方法（问题单/需求），并填写闭环单号（校验合法性）后进入闭环。</t>
+          <t>3. 评审通过则进入分析并由评审指派【责任人】；不通过则打回提出人修改。</t>
         </is>
       </c>
       <c r="B9" s="3" t="n"/>
@@ -699,7 +695,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>4. 每张【子单】独立走 闭环 → 子项验收；问题单走问题单闭环单、需求走需求闭环单。</t>
+          <t>4. 改进项分析：接纳后决定闭环方法（问题单/需求）并挂闭环单号（校验合法性）后进入闭环；不接纳则打回评审。</t>
         </is>
       </c>
       <c r="B10" s="3" t="n"/>
@@ -711,7 +707,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>5. 主单下全部【子单】子项验收通过后，进行【总项验收】；总项验收通过即完成（无独立归档环节）。</t>
+          <t>5. 责任人链：评审填写 → 分析继承 → 闭环继承。</t>
         </is>
       </c>
       <c r="B11" s="3" t="n"/>
@@ -720,235 +716,235 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>阶段</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>对应表单(Sheet)</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>目的</t>
-        </is>
-      </c>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6. 验收：谁提出谁验收，验收人=提出人，锁定不可转单；通过即完成。</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7. 闭环自测/验收结论支持富文本与粘贴图片；分析与闭环均有可逐条单独提交的【进展子项】，供外部审视。</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>关键判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>① 提出</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>1-提出-质量改进诉求单</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>记录诉求并列出全部子项</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>是否受理</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>② 评审</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>2-评审-评审记录单</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>逐项评审、生成子单</t>
+      <c r="F13" s="3" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>对应表单(Sheet)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>目的</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>通过/不通过</t>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>关键判定</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>③ 分析</t>
+          <t>① 提出</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>3-分析-改进项分析单</t>
+          <t>1-提出-质量改进诉求单</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>接纳与否、定闭环方法、挂闭环单号</t>
+          <t>记录诉求(关联yw系统单号)</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>是否接纳；闭环方法</t>
+          <t>是否受理</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>④a 闭环</t>
+          <t>② 评审</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>4-1闭环-问题单闭环单</t>
+          <t>2-评审-评审记录单</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>问题单:进展与效果自测</t>
+          <t>评审、指派责任人</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>进展/自测</t>
+          <t>通过/不通过(打回提出)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>④b 闭环</t>
+          <t>③ 分析</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>4-2闭环-需求闭环单</t>
+          <t>3-分析-改进项分析单</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>需求:进展与效果自测</t>
+          <t>接纳与否、定闭环方法、挂闭环单号</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>进展/自测</t>
+          <t>是否接纳(不接纳打回评审)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>⑤a 验收</t>
+          <t>④a 闭环</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>5-1-验收-子项验收单</t>
+          <t>4-1闭环-问题单闭环单</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>逐子单验收</t>
+          <t>问题单:进展与效果自测</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>验收是否通过</t>
+          <t>进展/自测/SLA</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>⑤b 验收</t>
+          <t>④b 闭环</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>5-2-验收-总项验收单</t>
+          <t>4-2闭环-需求闭环单</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>主单总体验收,通过即完成</t>
+          <t>需求:进展与效果自测</t>
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>总项验收是否通过</t>
+          <t>进展/自测/SLA</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>★ 跟踪</t>
+          <t>⑤ 验收</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>1.5-子单台账(中枢)</t>
+          <t>5-验收-验收单</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>汇总全部子单各环节进度</t>
+          <t>谁提出谁验收,通过即完成</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>主单是否具备总项验收条件</t>
+          <t>验收是否通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>★ 跟踪</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>1.5-改进诉求台账(中枢)</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>汇总各阶段进度</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>是否完成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="43">
     <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A22"/>
     <mergeCell ref="A17"/>
-    <mergeCell ref="C20:E20"/>
     <mergeCell ref="B15"/>
+    <mergeCell ref="C22:E22"/>
     <mergeCell ref="A20"/>
     <mergeCell ref="B20"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A13"/>
     <mergeCell ref="A19"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F14"/>
     <mergeCell ref="A15"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B16"/>
@@ -956,10 +952,11 @@
     <mergeCell ref="F19"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="F16"/>
+    <mergeCell ref="B22"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B18"/>
-    <mergeCell ref="C13:E13"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="B21"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="F15"/>
@@ -967,282 +964,19 @@
     <mergeCell ref="F21"/>
     <mergeCell ref="A16"/>
     <mergeCell ref="F20"/>
-    <mergeCell ref="B14"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="F18"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="C14:E14"/>
     <mergeCell ref="B17"/>
     <mergeCell ref="A18"/>
-    <mergeCell ref="B13"/>
     <mergeCell ref="F17"/>
     <mergeCell ref="A21"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="B19"/>
-    <mergeCell ref="A14"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F22"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="F13"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="64" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>填写约定与编号规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>一、填写类型（输入区底色）</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>用户填写</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>白底</t>
-        </is>
-      </c>
-      <c r="C3" s="21" t="inlineStr">
-        <is>
-          <t>由用户录入(必填/选填/条件必填)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>绿底(带『系统生成』)</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>系统自动生成/继承,用户免填(编号/状态/关联/日期/统计等)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>预填可改</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>紫底(带『预填·可改』)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>系统预填默认值(如验收人=提出人),用户可修改</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>二、编号规则</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>格式</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>主诉求单号</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>QI-YYYY-NNN</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>主单唯一编号,全流程主键</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>子项编号</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>01 / 02 / 03…</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>主单内子项序号</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>子单号</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>QI-YYYY-NNN-XX</t>
-        </is>
-      </c>
-      <c r="C11" s="21">
-        <f> 主诉求单号 + 子项序号;评审通过时生成</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>分析单号</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>AN-YYYY-NNN</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>改进项分析单编号(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>问题单号</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>PC-YYYY-NNN</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>问题单闭环单编号(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>需求单号</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>RC-YYYY-NNN</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>需求闭环单编号(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>子项验收单号</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>AC-YYYY-NNN</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>子项验收单编号(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>总项验收单号</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>系统生成,关联主单</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>总项验收单编号(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>三、流程：提出 → 评审(逐项通过→生成子单) → 改进项分析(接纳→定闭环方法) → 闭环(问题单/需求) → 验收(子项→总项,通过即完成)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1254,7 +988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1268,7 +1002,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>质量改进诉求单（提出阶段 · 可含多个子项）</t>
+          <t>质量改进诉求单（提出阶段）</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1117,7 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>诉求来源</t>
@@ -1391,8 +1125,12 @@
       </c>
       <c r="B12" s="12" t="inlineStr"/>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>关联yw系统单号</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr"/>
       <c r="F12" s="3" t="n"/>
     </row>
     <row r="13" ht="50" customHeight="1">
@@ -1410,7 +1148,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>四、改进子项明细（逐行一个子项；评审后将按子项生成子单）</t>
+          <t>四、审批</t>
         </is>
       </c>
       <c r="B15" s="3" t="n"/>
@@ -1419,222 +1157,42 @@
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>子项编号</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>子项标题</t>
-        </is>
-      </c>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>审批人(固定下拉名单)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr"/>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>子项简述/现象</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>五、审批</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>审批人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A17"/>
-    <mergeCell ref="D18"/>
-    <mergeCell ref="A22"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="A20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E16"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A19"/>
-    <mergeCell ref="E22"/>
+  <mergeCells count="15">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="E18"/>
-    <mergeCell ref="D20"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="E21"/>
-    <mergeCell ref="D19"/>
-    <mergeCell ref="F19"/>
-    <mergeCell ref="F16"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D22"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="E17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="E20"/>
-    <mergeCell ref="D21"/>
-    <mergeCell ref="F21"/>
-    <mergeCell ref="A16"/>
-    <mergeCell ref="E19"/>
-    <mergeCell ref="F20"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="F18"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A18"/>
-    <mergeCell ref="D17"/>
-    <mergeCell ref="F17"/>
-    <mergeCell ref="A21"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="D16"/>
-    <mergeCell ref="F22"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
-  <dataValidations count="13">
+  <dataValidations count="2">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"现网问题,客户提出,实验室发现"</formula1>
     </dataValidation>
-    <dataValidation sqref="D17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"问题单,需求"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"高,中,低"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"问题单,需求"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"高,中,低"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"问题单,需求"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"高,中,低"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"问题单,需求"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"高,中,低"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"问题单,需求"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"高,中,低"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"问题单,需求"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"高,中,低"</formula1>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"张三(10001),李四(10002),王五(10003)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1647,65 +1205,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>子单台账（中枢 · 汇总全部子单在各环节的进度）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
+          <t>改进诉求台账（中枢 · 汇总各阶段进度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>一张主诉求单拆为多张子单,每张子单独立流转;本表以子单为单位汇总各阶段结果与状态。全部子单『子项验收·是否通过』为通过后,主单可进行总项验收。</t>
+          <t>一张主诉求单即一项改进措施,单链流转;本表汇总其在各阶段的结果与状态。『验收·是否通过』为通过即完成。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>子单号</t>
+          <t>主诉求单号</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>父诉求单号</t>
+          <t>提出人</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>子项编号</t>
+          <t>诉求来源</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>关联yw系统单号</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>责任人/部门</t>
+          <t>评审结果</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>评审结果</t>
+          <t>责任人</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -1725,10 +1284,15 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>子项验收·是否通过</t>
+          <t>SLA时间</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>验收·是否通过</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>当前状态</t>
         </is>
@@ -1737,55 +1301,60 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>QI-2026-001-01</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
           <t>QI-2026-001</t>
         </is>
       </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>张三/工艺部</t>
+        </is>
+      </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>现网问题</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>问题单</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>张工/工艺部</t>
+          <t>YW-2026-007</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
+          <t>张工</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>问题单闭环</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>PC-2026-001</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>问题单闭环</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>PC-2026-001</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -1794,32 +1363,32 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>QI-2026-001-02</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>QI-2026-001</t>
+          <t>QI-2026-002</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>李四/研发部</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>客户提出</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>需求</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>李工/研发部</t>
+          <t>YW-2026-019</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>李工</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -1834,15 +1403,20 @@
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>RC-2026-001</t>
+          <t>RC-2026-002</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
           <t>待验收</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>待验收</t>
         </is>
@@ -1851,32 +1425,32 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>QI-2026-001-03</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>QI-2026-001</t>
+          <t>QI-2026-003</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>王五/质量部</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>实验室发现</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>问题单</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>王工/质量部</t>
+          <t>YW-2026-031</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>不通过</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>不通过</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -1900,6 +1474,11 @@
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>已驳回</t>
         </is>
@@ -1917,6 +1496,7 @@
       <c r="I7" s="16" t="n"/>
       <c r="J7" s="16" t="n"/>
       <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="16" t="n"/>
@@ -1930,6 +1510,7 @@
       <c r="I8" s="16" t="n"/>
       <c r="J8" s="16" t="n"/>
       <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="16" t="n"/>
@@ -1943,6 +1524,7 @@
       <c r="I9" s="16" t="n"/>
       <c r="J9" s="16" t="n"/>
       <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="16" t="n"/>
@@ -1956,6 +1538,7 @@
       <c r="I10" s="16" t="n"/>
       <c r="J10" s="16" t="n"/>
       <c r="K10" s="16" t="n"/>
+      <c r="L10" s="16" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="16" t="n"/>
@@ -1969,6 +1552,7 @@
       <c r="I11" s="16" t="n"/>
       <c r="J11" s="16" t="n"/>
       <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="16" t="n"/>
@@ -1982,6 +1566,7 @@
       <c r="I12" s="16" t="n"/>
       <c r="J12" s="16" t="n"/>
       <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="16" t="n"/>
@@ -1995,6 +1580,7 @@
       <c r="I13" s="16" t="n"/>
       <c r="J13" s="16" t="n"/>
       <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="16" t="n"/>
@@ -2008,19 +1594,20 @@
       <c r="I14" s="16" t="n"/>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>注：浅色行为示例数据,实际使用时替换或删除。子单号 = 父诉求单号 + 子项序号。</t>
+          <t>注：浅色行为示例数据,实际使用时替换或删除。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2032,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2046,14 +1633,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>评审记录单（评审阶段 · 逐项评审,通过则生成子单）</t>
+          <t>评审记录单（评审阶段 · 通过则进入分析并指派责任人）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联主诉求单号    评审通过则生成子单进入分析,不通过则该子项终止</t>
+          <t>关联主诉求单号    评审通过则进入分析并指派责任人;不通过则打回提出人修改</t>
         </is>
       </c>
     </row>
@@ -2120,7 +1707,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>二、子项拆单分发表（逐项评审；子项内容继承自提出单,此处只判定通过与否）</t>
+          <t>二、评审结论</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -2129,223 +1716,50 @@
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>子项编号</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>评审结果</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>不通过理由</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>生成子单号</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>责任人/部门</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
+      <c r="B8" s="12" t="inlineStr"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>责任人(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>不通过理由（评审结果为『不通过』时必填）</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr"/>
+      <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="n"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="n"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="n"/>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="n"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>三、统计</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>拆单总数(张)</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="A8"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B9"/>
-    <mergeCell ref="F9"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A10"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A13"/>
-    <mergeCell ref="F14"/>
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E12"/>
-    <mergeCell ref="F11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F10"/>
-    <mergeCell ref="A11"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="E14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E8"/>
-    <mergeCell ref="B12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F12"/>
-    <mergeCell ref="B11"/>
-    <mergeCell ref="E10"/>
-    <mergeCell ref="B14"/>
-    <mergeCell ref="E13"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B8"/>
-    <mergeCell ref="E9"/>
-    <mergeCell ref="F8"/>
-    <mergeCell ref="A12"/>
-    <mergeCell ref="B13"/>
+    <mergeCell ref="B9:F9"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B10"/>
-    <mergeCell ref="E11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A14"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="F13"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,不通过"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2373,14 +1787,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>改进项分析单（分析阶段 · 针对单张子单）</t>
+          <t>改进项分析单（分析阶段）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：子单号 + 父诉求单号    接纳后填写闭环单号(校验合法性)方可进入闭环;不接纳则终止</t>
+          <t>关联：主诉求单号    接纳后填写闭环单号(校验合法性)进入闭环;不接纳则打回评审</t>
         </is>
       </c>
     </row>
@@ -2410,7 +1824,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>关联子单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -2423,7 +1837,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>父诉求单号</t>
+          <t>分析日期</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -2434,7 +1848,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>分析日期</t>
+          <t>责任人(工号+姓名)</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -2507,7 +1921,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>不接纳理由（是否接纳为『否』时必填）</t>
+          <t>不接纳理由（是否接纳为『否』时必填,否则打回评审）</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr"/>
@@ -2519,7 +1933,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>三、闭环单号（必填,需校验合法性）</t>
+          <t>三、闭环单号（接纳后必填,需校验合法性）</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -2762,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2776,14 +2190,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>问题单闭环单（闭环 · 问题单路径 · 针对单张子单）</t>
+          <t>问题单闭环单（闭环 · 问题单路径）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：子单号 + 父诉求单号 + 分析单号    只关注当前进展与闭环效果自测</t>
+          <t>关联：主诉求单号 + 分析单号    关注当前进展与闭环效果自测</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2227,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>关联子单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -2826,7 +2240,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>父诉求单号</t>
+          <t>关联分析单号</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -2837,7 +2251,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>关联分析单号</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -2861,7 +2275,7 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>当前状态</t>
+          <t>责任人(工号+姓名)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -2871,25 +2285,25 @@
       </c>
       <c r="F6" s="3" t="n"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>SLA时间（闭环完成时限,由闭环人填写可改）</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>二、进展与自测</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>当前进展</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr"/>
+      <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
@@ -2898,7 +2312,7 @@
     <row r="10" ht="50" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>闭环效果自测</t>
+          <t>当前进展</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr"/>
@@ -2907,59 +2321,51 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>闭环效果自测（富文本,可粘贴图片）</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>三、进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>进展说明</t>
-        </is>
-      </c>
+      <c r="B13" s="3" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>提交人</t>
         </is>
       </c>
     </row>
@@ -3063,37 +2469,59 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="42">
+    <mergeCell ref="B7:F7"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="A17"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A20"/>
     <mergeCell ref="E16"/>
-    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A13"/>
     <mergeCell ref="A19"/>
     <mergeCell ref="F14"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E18"/>
+    <mergeCell ref="B11:F11"/>
     <mergeCell ref="A15"/>
-    <mergeCell ref="A8:F8"/>
     <mergeCell ref="F19"/>
     <mergeCell ref="F16"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="E14"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E17"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="B10:F10"/>
+    <mergeCell ref="E20"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="F15"/>
     <mergeCell ref="A16"/>
     <mergeCell ref="E19"/>
-    <mergeCell ref="E13"/>
-    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="F20"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="F18"/>
     <mergeCell ref="B6:C6"/>
@@ -3105,7 +2533,6 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A14"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3117,7 +2544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3131,14 +2558,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>需求闭环单（闭环 · 需求路径 · 针对单张子单）</t>
+          <t>需求闭环单（闭环 · 需求路径）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：子单号 + 父诉求单号 + 分析单号    只关注当前进展与闭环效果自测</t>
+          <t>关联：主诉求单号 + 分析单号    关注当前进展与闭环效果自测</t>
         </is>
       </c>
     </row>
@@ -3168,7 +2595,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>关联子单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -3181,7 +2608,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>父诉求单号</t>
+          <t>关联分析单号</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -3192,7 +2619,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>关联分析单号</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -3216,7 +2643,7 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>当前状态</t>
+          <t>责任人(工号+姓名)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3226,25 +2653,25 @@
       </c>
       <c r="F6" s="3" t="n"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>SLA时间（闭环完成时限,由闭环人填写可改）</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>二、进展与自测</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>当前进展</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr"/>
+      <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
@@ -3253,7 +2680,7 @@
     <row r="10" ht="50" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>闭环效果自测</t>
+          <t>当前进展</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr"/>
@@ -3262,59 +2689,51 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>闭环效果自测（富文本,可粘贴图片）</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>三、进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>进展说明</t>
-        </is>
-      </c>
+      <c r="B13" s="3" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>提交人</t>
         </is>
       </c>
     </row>
@@ -3418,37 +2837,59 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="42">
+    <mergeCell ref="B7:F7"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="A17"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A20"/>
     <mergeCell ref="E16"/>
-    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A13"/>
     <mergeCell ref="A19"/>
     <mergeCell ref="F14"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E18"/>
+    <mergeCell ref="B11:F11"/>
     <mergeCell ref="A15"/>
-    <mergeCell ref="A8:F8"/>
     <mergeCell ref="F19"/>
     <mergeCell ref="F16"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="E14"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E17"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="B10:F10"/>
+    <mergeCell ref="E20"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="F15"/>
     <mergeCell ref="A16"/>
     <mergeCell ref="E19"/>
-    <mergeCell ref="E13"/>
-    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="F20"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="F18"/>
     <mergeCell ref="B6:C6"/>
@@ -3460,7 +2901,6 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A14"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3486,14 +2926,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>子项验收单（针对单张子单;全部子单通过后进入总项验收）</t>
+          <t>验收单（谁提出谁验收,不可转单）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：子单号 + 父诉求单号 + 闭环单号</t>
+          <t>关联：主诉求单号 + 闭环单号    验收人=改进提出人,系统生成,锁定不可转单</t>
         </is>
       </c>
     </row>
@@ -3523,7 +2963,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>关联子单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -3536,7 +2976,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>父诉求单号</t>
+          <t>关联闭环单号</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -3547,7 +2987,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>关联闭环单号</t>
+          <t>验收人(工号+姓名)</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -3557,28 +2997,20 @@
       </c>
       <c r="F5" s="3" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>验收人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>(预填·可改)</t>
+          <t>当前状态</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -3593,10 +3025,10 @@
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
     </row>
-    <row r="9" ht="50" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>验收结论</t>
+          <t>验收结论（富文本,可粘贴图片）</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr"/>
@@ -3618,12 +3050,11 @@
       <c r="F10" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B10:F10"/>
@@ -3647,175 +3078,223 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>总项验收单（主单下全部子项验收通过后进行,通过即完成）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>关联：主诉求单号</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>一、单据信息</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>总项验收单号</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>关联主诉求单号</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>验收人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>(预填·可改)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
+          <t>填写约定与编号规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>一、填写类型（输入区底色）</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>用户填写</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>白底</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>由用户录入(必填/选填/条件必填)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>绿底(带『系统生成』)</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>系统自动生成/继承,用户免填(编号/状态/关联/日期/责任人继承/提交人等)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>预填可改</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>紫底(带『预填·可改』)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>系统预填默认值,用户可修改</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>二、子项验收状态（系统生成,只读）</t>
+          <t>二、编号规则</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>各子项验收状态</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>三、总项验收结论</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>总项验收结论</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>格式</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>主诉求单号</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>QI-YYYY-NNN</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>主单唯一编号,全流程主键</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>分析单号</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>AN-YYYY-NNN</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>改进项分析单编号(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>问题单号</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>PC-YYYY-NNN</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>问题单闭环单编号(系统生成)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>总项验收是否通过</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>需求单号</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>RC-YYYY-NNN</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>需求闭环单编号(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>验收单号</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>AC-YYYY-NNN</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>验收单编号(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>关联yw系统单号</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>YW-YYYY-NNN</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>提出单关联的业务系统原始单号(用户填写)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>三、其他约定：审批人为固定下拉名单(系统配置);闭环自测/验收结论支持富文本与粘贴图片;责任人 评审填写→分析继承→闭环继承;验收人=提出人,锁定不可转单。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/质量改进诉求流程表单.xlsx
+++ b/质量改进诉求流程表单.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>记录诉求(关联yw系统单号)</t>
+          <t>记录诉求(关联运维系统单号)</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -1108,7 +1108,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>诉求总体标题</t>
+          <t>诉求标题</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr"/>
@@ -1117,26 +1117,22 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
     </row>
-    <row r="12" ht="24" customHeight="1">
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>诉求来源</t>
+          <t>关联运维系统单号</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr"/>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>关联yw系统单号</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
     </row>
-    <row r="13" ht="50" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>总体背景与目标（问题概述、影响、期望达成）</t>
+          <t>诉求描述（富文本,可粘贴图片）</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr"/>
@@ -1148,7 +1144,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>四、审批</t>
+          <t>四、评审人（固定下拉名单）</t>
         </is>
       </c>
       <c r="B15" s="3" t="n"/>
@@ -1160,7 +1156,7 @@
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>审批人(固定下拉名单)</t>
+          <t>评审人(工号+姓名)</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr"/>
@@ -1170,10 +1166,10 @@
       <c r="F16" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A1:F1"/>
@@ -1185,12 +1181,8 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"现网问题,客户提出,实验室发现"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"张三(10001),李四(10002),王五(10003)"</formula1>
     </dataValidation>
@@ -1205,21 +1197,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1249,50 +1240,45 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>诉求来源</t>
+          <t>关联运维系统单号</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>关联yw系统单号</t>
+          <t>评审结果</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>评审结果</t>
+          <t>责任人</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>责任人</t>
+          <t>分析·是否接纳</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>分析·是否接纳</t>
+          <t>闭环方法</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>闭环方法</t>
+          <t>闭环单号</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>闭环单号</t>
+          <t>SLA时间</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>SLA时间</t>
+          <t>验收·是否通过</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>验收·是否通过</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>当前状态</t>
         </is>
@@ -1311,50 +1297,45 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>现网问题</t>
+          <t>YW-2026-007</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>YW-2026-007</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
+          <t>张工</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>问题单闭环</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>PC-2026-001</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>张工</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>问题单闭环</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>PC-2026-001</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
       <c r="K4" s="14" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -1373,50 +1354,45 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>客户提出</t>
+          <t>YW-2026-019</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>YW-2026-019</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>李工</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>李工</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>需求闭环</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>需求闭环</t>
+          <t>RC-2026-002</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>RC-2026-002</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>待验收</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>待验收</t>
-        </is>
-      </c>
-      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>待验收</t>
         </is>
@@ -1435,17 +1411,17 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>实验室发现</t>
+          <t>YW-2026-031</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>YW-2026-031</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>不通过</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1474,11 +1450,6 @@
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>已驳回</t>
         </is>
@@ -1496,7 +1467,6 @@
       <c r="I7" s="16" t="n"/>
       <c r="J7" s="16" t="n"/>
       <c r="K7" s="16" t="n"/>
-      <c r="L7" s="16" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="16" t="n"/>
@@ -1510,7 +1480,6 @@
       <c r="I8" s="16" t="n"/>
       <c r="J8" s="16" t="n"/>
       <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="16" t="n"/>
@@ -1524,7 +1493,6 @@
       <c r="I9" s="16" t="n"/>
       <c r="J9" s="16" t="n"/>
       <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="16" t="n"/>
@@ -1538,7 +1506,6 @@
       <c r="I10" s="16" t="n"/>
       <c r="J10" s="16" t="n"/>
       <c r="K10" s="16" t="n"/>
-      <c r="L10" s="16" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="16" t="n"/>
@@ -1552,7 +1519,6 @@
       <c r="I11" s="16" t="n"/>
       <c r="J11" s="16" t="n"/>
       <c r="K11" s="16" t="n"/>
-      <c r="L11" s="16" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="16" t="n"/>
@@ -1566,7 +1532,6 @@
       <c r="I12" s="16" t="n"/>
       <c r="J12" s="16" t="n"/>
       <c r="K12" s="16" t="n"/>
-      <c r="L12" s="16" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="16" t="n"/>
@@ -1580,7 +1545,6 @@
       <c r="I13" s="16" t="n"/>
       <c r="J13" s="16" t="n"/>
       <c r="K13" s="16" t="n"/>
-      <c r="L13" s="16" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="16" t="n"/>
@@ -1594,7 +1558,6 @@
       <c r="I14" s="16" t="n"/>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -1605,9 +1568,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3267,7 +3230,7 @@
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>关联yw系统单号</t>
+          <t>关联运维系统单号</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
@@ -3277,14 +3240,14 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>提出单关联的业务系统原始单号(用户填写)</t>
+          <t>提出单关联的运维系统单号(用户填写)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>三、其他约定：审批人为固定下拉名单(系统配置);闭环自测/验收结论支持富文本与粘贴图片;责任人 评审填写→分析继承→闭环继承;验收人=提出人,锁定不可转单。</t>
+          <t>三、其他约定：评审人为固定下拉名单(系统配置);诉求描述/闭环自测/验收结论支持富文本与粘贴图片;责任人 评审填写→分析继承→闭环继承;验收人=提出人,锁定不可转单。</t>
         </is>
       </c>
     </row>

--- a/质量改进诉求流程表单.xlsx
+++ b/质量改进诉求流程表单.xlsx
@@ -1873,12 +1873,8 @@
       </c>
       <c r="B10" s="12" t="inlineStr"/>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>计划完成期限</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
@@ -2074,7 +2070,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="44">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A22"/>
     <mergeCell ref="A17"/>
@@ -2089,7 +2085,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E18"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="E21"/>
     <mergeCell ref="A8:F8"/>
@@ -2100,8 +2095,8 @@
     <mergeCell ref="E23"/>
     <mergeCell ref="E17"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="E20"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="F21"/>
     <mergeCell ref="E19"/>
     <mergeCell ref="F20"/>

--- a/质量改进诉求流程表单.xlsx
+++ b/质量改进诉求流程表单.xlsx
@@ -12,10 +12,9 @@
     <sheet name="1.5-改进诉求台账(中枢)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2-评审-评审记录单" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="3-分析-改进项分析单" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4-1闭环-问题单闭环单" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="4-2闭环-需求闭环单" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5-验收-验收单" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="6-填写约定与编号规则" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="4-闭环单" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5-验收-验收单" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6-填写约定与编号规则" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -602,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -635,7 +634,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>单链流程（不拆子项）；④ 闭环含两条路径：问题单闭环（缺陷/故障纠正预防）｜ 需求闭环（新功能/优化上线）</t>
+          <t>单链流程（不拆子项）；④ 闭环单合一,由闭环方式(问题单闭环/需求闭环)决定单号前缀 PC-/RC-</t>
         </is>
       </c>
       <c r="B4" s="3" t="n"/>
@@ -839,106 +838,80 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>④a 闭环</t>
+          <t>④ 闭环</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>4-1闭环-问题单闭环单</t>
+          <t>4-闭环单</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>问题单:进展与效果自测</t>
+          <t>由闭环方式决定单号;进展与效果自测</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>进展/自测/SLA</t>
+          <t>进展/自测/SLA/闭环方式</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>④b 闭环</t>
+          <t>⑤ 验收</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>4-2闭环-需求闭环单</t>
+          <t>5-验收-验收单</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>需求:进展与效果自测</t>
+          <t>谁提出谁验收,通过即完成</t>
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>进展/自测/SLA</t>
+          <t>验收是否通过</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>⑤ 验收</t>
+          <t>★ 跟踪</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>5-验收-验收单</t>
+          <t>1.5-改进诉求台账(中枢)</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>谁提出谁验收,通过即完成</t>
+          <t>汇总各阶段进度</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>验收是否通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>★ 跟踪</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>1.5-改进诉求台账(中枢)</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>汇总各阶段进度</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
           <t>是否完成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="39">
     <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A22"/>
     <mergeCell ref="A17"/>
     <mergeCell ref="B15"/>
-    <mergeCell ref="C22:E22"/>
     <mergeCell ref="A20"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="A12:F12"/>
@@ -952,7 +925,6 @@
     <mergeCell ref="F19"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="F16"/>
-    <mergeCell ref="B22"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B18"/>
     <mergeCell ref="C19:E19"/>
@@ -975,7 +947,6 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="B19"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F22"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2148,14 +2119,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>问题单闭环单（闭环 · 问题单路径）</t>
+          <t>闭环单（闭环阶段 · 由闭环方式决定单号前缀）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：主诉求单号 + 分析单号    关注当前进展与闭环效果自测</t>
+          <t>关联：主诉求单号 + 分析单号    闭环方式:问题单闭环→PC- / 需求闭环→RC-</t>
         </is>
       </c>
     </row>
@@ -2174,18 +2145,14 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>问题单号</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
+          <t>闭环方式</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>关联主诉求单号</t>
+          <t>闭环单号</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -2198,7 +2165,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>关联分析单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -2209,7 +2176,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>当前状态</t>
+          <t>关联分析单号</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -2222,7 +2189,7 @@
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>闭环类型</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -2492,379 +2459,16 @@
     <mergeCell ref="A14"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"问题单闭环,需求闭环"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>需求闭环单（闭环 · 需求路径）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>关联：主诉求单号 + 分析单号    关注当前进展与闭环效果自测</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>一、单据信息</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>需求单号</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>关联主诉求单号</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>关联分析单号</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>闭环类型</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>责任人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>SLA时间（闭环完成时限,由闭环人填写可改）</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>二、进展与自测</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>当前进展</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>闭环效果自测（富文本,可粘贴图片）</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>三、进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="A17"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A20"/>
-    <mergeCell ref="E16"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A19"/>
-    <mergeCell ref="F14"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E18"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A15"/>
-    <mergeCell ref="F19"/>
-    <mergeCell ref="F16"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E14"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E17"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="E20"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="F15"/>
-    <mergeCell ref="A16"/>
-    <mergeCell ref="E19"/>
-    <mergeCell ref="F20"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F18"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A18"/>
-    <mergeCell ref="F17"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E15"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A14"/>
-    <mergeCell ref="B4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3030,13 +2634,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3174,73 +2778,56 @@
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>问题单号</t>
+          <t>闭环单号</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>PC-YYYY-NNN</t>
+          <t>PC-YYYY-NNN / RC-YYYY-NNN</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>问题单闭环单编号(系统生成)</t>
+          <t>闭环单编号(系统生成,前缀随闭环方式)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>需求单号</t>
+          <t>验收单号</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>RC-YYYY-NNN</t>
+          <t>AC-YYYY-NNN</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>需求闭环单编号(系统生成)</t>
+          <t>验收单编号(系统生成)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>验收单号</t>
+          <t>关联运维系统单号</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>AC-YYYY-NNN</t>
+          <t>YW-YYYY-NNN</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>验收单编号(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>关联运维系统单号</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>YW-YYYY-NNN</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
           <t>提出单关联的运维系统单号(用户填写)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>三、其他约定：评审人为固定下拉名单(系统配置);诉求描述/闭环自测/验收结论支持富文本与粘贴图片;责任人 评审填写→分析继承→闭环继承;验收人=提出人,锁定不可转单。</t>
         </is>
@@ -3251,7 +2838,7 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/质量改进诉求流程表单.xlsx
+++ b/质量改进诉求流程表单.xlsx
@@ -2126,7 +2126,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：主诉求单号 + 分析单号    闭环方式:问题单闭环→PC- / 需求闭环→RC-</t>
+          <t>关联：主诉求单号 + 分析单号    闭环方法与单号均由分析阶段继承</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,11 @@
           <t>闭环方式</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr"/>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
@@ -2459,11 +2463,6 @@
     <mergeCell ref="A14"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"问题单闭环,需求闭环"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/质量改进诉求流程表单.xlsx
+++ b/质量改进诉求流程表单.xlsx
@@ -2105,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2238,10 +2238,10 @@
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
     </row>
-    <row r="10" ht="50" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>当前进展</t>
+          <t>闭环效果自测（富文本,可粘贴图片）</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr"/>
@@ -2250,51 +2250,59 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>闭环效果自测（富文本,可粘贴图片）</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>三、进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>进展说明</t>
-        </is>
-      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>提交人</t>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
         </is>
       </c>
     </row>
@@ -2398,59 +2406,37 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="41">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="A17"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A20"/>
+    <mergeCell ref="B13:D13"/>
     <mergeCell ref="E16"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A13"/>
     <mergeCell ref="A19"/>
     <mergeCell ref="F14"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E18"/>
-    <mergeCell ref="B11:F11"/>
     <mergeCell ref="A15"/>
     <mergeCell ref="F19"/>
     <mergeCell ref="F16"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="E14"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E17"/>
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="E20"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="F15"/>
     <mergeCell ref="A16"/>
     <mergeCell ref="E19"/>
-    <mergeCell ref="F20"/>
+    <mergeCell ref="E13"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="F18"/>
     <mergeCell ref="B6:C6"/>
@@ -2462,6 +2448,7 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A14"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2494,7 +2481,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：主诉求单号 + 闭环单号    验收人=改进提出人,系统生成,锁定不可转单</t>
+          <t>关联：主诉求单号 + 闭环单号    验收人=改进提出人;不通过则打回闭环(截图贴入验收结论)</t>
         </is>
       </c>
     </row>

--- a/质量改进诉求流程表单.xlsx
+++ b/质量改进诉求流程表单.xlsx
@@ -622,7 +622,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>① 提出  ➜  ② 评审(通过→指派责任人;不通过→打回提出)  ➜  ③ 改进项分析(接纳→定闭环方法→挂闭环单号;不接纳→打回评审)  ➜  ④ 闭环(问题单/需求)  ➜  ⑤ 验收(谁提出谁验收,通过即完成)</t>
+          <t>① 提出  ➜  ② 评审(通过→指派责任人;不通过→打回提出)  ➜  ③ 改进项分析(接纳→定闭环方法;不接纳→打回评审)  ➜  ④ 闭环(闭环方式继承自分析)  ➜  ⑤ 验收(谁提出谁验收,通过即完成)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
@@ -694,7 +694,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>4. 改进项分析：接纳后决定闭环方法（问题单/需求）并挂闭环单号（校验合法性）后进入闭环；不接纳则打回评审。</t>
+          <t>4. 改进项分析：接纳后决定闭环方法（问题单/需求）进入闭环；不接纳则打回评审。</t>
         </is>
       </c>
       <c r="B10" s="3" t="n"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>接纳与否、定闭环方法、挂闭环单号</t>
+          <t>接纳与否、定闭环方法</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
@@ -1168,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1178,10 +1178,9 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1236,20 +1235,15 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>闭环单号</t>
+          <t>SLA时间</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>SLA时间</t>
+          <t>验收·是否通过</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>验收·是否通过</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>当前状态</t>
         </is>
@@ -1293,20 +1287,15 @@
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>PC-2026-001</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -1350,20 +1339,15 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>RC-2026-002</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>待验收</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
-        <is>
-          <t>待验收</t>
-        </is>
-      </c>
-      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>待验收</t>
         </is>
@@ -1416,11 +1400,6 @@
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>已驳回</t>
         </is>
@@ -1437,7 +1416,6 @@
       <c r="H7" s="16" t="n"/>
       <c r="I7" s="16" t="n"/>
       <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="16" t="n"/>
@@ -1450,7 +1428,6 @@
       <c r="H8" s="16" t="n"/>
       <c r="I8" s="16" t="n"/>
       <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="16" t="n"/>
@@ -1463,7 +1440,6 @@
       <c r="H9" s="16" t="n"/>
       <c r="I9" s="16" t="n"/>
       <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="16" t="n"/>
@@ -1476,7 +1452,6 @@
       <c r="H10" s="16" t="n"/>
       <c r="I10" s="16" t="n"/>
       <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="16" t="n"/>
@@ -1489,7 +1464,6 @@
       <c r="H11" s="16" t="n"/>
       <c r="I11" s="16" t="n"/>
       <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="16" t="n"/>
@@ -1502,7 +1476,6 @@
       <c r="H12" s="16" t="n"/>
       <c r="I12" s="16" t="n"/>
       <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="16" t="n"/>
@@ -1515,7 +1488,6 @@
       <c r="H13" s="16" t="n"/>
       <c r="I13" s="16" t="n"/>
       <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="16" t="n"/>
@@ -1528,7 +1500,6 @@
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n"/>
       <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -1539,9 +1510,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1593,7 +1564,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>评审单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -1602,16 +1573,8 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>关联主诉求单号</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
@@ -1679,17 +1642,16 @@
       <c r="F9" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
+    <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E4:F4"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <dataValidations count="1">
@@ -1707,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1728,7 +1690,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：主诉求单号    接纳后填写闭环单号(校验合法性)进入闭环;不接纳则打回评审</t>
+          <t>关联：主诉求单号    接纳后进入闭环;不接纳则打回评审</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1709,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>分析单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -1758,7 +1720,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>关联主诉求单号</t>
+          <t>分析日期</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -1771,7 +1733,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>分析日期</t>
+          <t>责任人(工号+姓名)</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -1780,16 +1742,8 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>责任人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1863,7 +1817,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>三、闭环单号（接纳后必填,需校验合法性）</t>
+          <t>三、分析进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -1872,51 +1826,87 @@
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>问题单号/需求单号</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr"/>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>四、分析进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>进展说明</t>
-        </is>
-      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>提交人</t>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
         </is>
       </c>
     </row>
@@ -1980,112 +1970,49 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A22"/>
+  <mergeCells count="41">
+    <mergeCell ref="B14:D14"/>
     <mergeCell ref="A17"/>
-    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E5:F5"/>
     <mergeCell ref="A20"/>
+    <mergeCell ref="E16"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A19"/>
-    <mergeCell ref="E22"/>
+    <mergeCell ref="F14"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E18"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="E21"/>
+    <mergeCell ref="A15"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="F19"/>
-    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="F16"/>
+    <mergeCell ref="B15:D15"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E14"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E23"/>
     <mergeCell ref="E17"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="E20"/>
-    <mergeCell ref="F21"/>
+    <mergeCell ref="F15"/>
+    <mergeCell ref="A16"/>
     <mergeCell ref="E19"/>
     <mergeCell ref="F20"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="F18"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A18"/>
     <mergeCell ref="F17"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A21"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="E15"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F23"/>
-    <mergeCell ref="F22"/>
+    <mergeCell ref="A14"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A23"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2119,14 +2046,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>闭环单（闭环阶段 · 由闭环方式决定单号前缀）</t>
+          <t>闭环单（闭环阶段 · 闭环方式由分析阶段继承）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：主诉求单号 + 分析单号    闭环方法与单号均由分析阶段继承</t>
+          <t>关联：主诉求单号    闭环方式由分析阶段继承,通过即进入验收</t>
         </is>
       </c>
     </row>
@@ -2154,16 +2081,8 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>闭环单号</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
@@ -2178,16 +2097,8 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>关联分析单号</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
@@ -2407,12 +2318,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="39">
+    <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="A17"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E5:F5"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E16"/>
     <mergeCell ref="A12:F12"/>
@@ -2421,7 +2332,6 @@
     <mergeCell ref="A19"/>
     <mergeCell ref="F14"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E4:F4"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E18"/>
     <mergeCell ref="A15"/>
@@ -2442,12 +2352,11 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A18"/>
     <mergeCell ref="F17"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="E15"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A14"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2481,7 +2390,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：主诉求单号 + 闭环单号    验收人=改进提出人;不通过则打回闭环(截图贴入验收结论)</t>
+          <t>关联：主诉求单号    验收人=改进提出人;不通过则打回闭环(截图贴入验收结论)</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2409,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>验收单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -2509,22 +2418,14 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>关联主诉求单号</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>关联闭环单号</t>
+          <t>验收人(工号+姓名)</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -2533,16 +2434,8 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>验收人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -2598,18 +2491,16 @@
       <c r="F10" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="9">
+    <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2626,7 +2517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2740,80 +2631,29 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>主单唯一编号,全流程主键</t>
+          <t>主单唯一编号,全流程主键(诉求单号贯穿全程)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>分析单号</t>
+          <t>关联运维系统单号</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>AN-YYYY-NNN</t>
+          <t>YW-YYYY-NNN</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>改进项分析单编号(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>闭环单号</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>PC-YYYY-NNN / RC-YYYY-NNN</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>闭环单编号(系统生成,前缀随闭环方式)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>验收单号</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>AC-YYYY-NNN</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>验收单编号(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>关联运维系统单号</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>YW-YYYY-NNN</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
           <t>提出单关联的运维系统单号(用户填写)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>三、其他约定：评审人为固定下拉名单(系统配置);诉求描述/闭环自测/验收结论支持富文本与粘贴图片;责任人 评审填写→分析继承→闭环继承;验收人=提出人,锁定不可转单。</t>
         </is>
@@ -2824,7 +2664,7 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/质量改进诉求流程表单.xlsx
+++ b/质量改进诉求流程表单.xlsx
@@ -622,7 +622,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>① 提出  ➜  ② 评审(通过→指派责任人;不通过→打回提出)  ➜  ③ 改进项分析(接纳→定闭环方法;不接纳→打回评审)  ➜  ④ 闭环(闭环方式继承自分析)  ➜  ⑤ 验收(谁提出谁验收,通过即完成)</t>
+          <t>① 提出  ➜  ② 评审(通过→指派责任人;不通过→打回提出)  ➜  ③ 改进项分析(接纳→定闭环方法→挂闭环单号;不接纳→打回评审)  ➜  ④ 闭环(闭环方式继承自分析)  ➜  ⑤ 验收(谁提出谁验收,通过即完成)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
@@ -694,7 +694,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>4. 改进项分析：接纳后决定闭环方法（问题单/需求）进入闭环；不接纳则打回评审。</t>
+          <t>4. 改进项分析：接纳后决定闭环方法（问题单/需求）并挂闭环单号（校验合法性）后进入闭环；不接纳则打回评审。</t>
         </is>
       </c>
       <c r="B10" s="3" t="n"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>接纳与否、定闭环方法</t>
+          <t>接纳与否、定闭环方法、挂闭环单号</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
@@ -1669,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1690,7 +1690,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：主诉求单号    接纳后进入闭环;不接纳则打回评审</t>
+          <t>关联：主诉求单号    接纳后填写闭环单号(校验合法性)进入闭环;不接纳则打回评审</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>三、分析进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
+          <t>三、闭环单号（接纳后必填,需校验合法性）</t>
         </is>
       </c>
       <c r="B13" s="3" t="n"/>
@@ -1826,87 +1826,51 @@
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>进展说明</t>
-        </is>
-      </c>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>问题单号/需求单号</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>四、分析进展子项（可逐条单独提交,作为外部审视进展的依据）</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>(系统生成)</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>提交人</t>
         </is>
       </c>
     </row>
@@ -1970,49 +1934,111 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="B14:D14"/>
+  <mergeCells count="43">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A22"/>
     <mergeCell ref="A17"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="A20"/>
-    <mergeCell ref="E16"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A19"/>
-    <mergeCell ref="F14"/>
+    <mergeCell ref="E22"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E18"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A15"/>
+    <mergeCell ref="E21"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="F19"/>
-    <mergeCell ref="F16"/>
-    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E14"/>
     <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E23"/>
     <mergeCell ref="E17"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="E20"/>
-    <mergeCell ref="F15"/>
-    <mergeCell ref="A16"/>
+    <mergeCell ref="F21"/>
     <mergeCell ref="E19"/>
     <mergeCell ref="F20"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="F18"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A18"/>
     <mergeCell ref="F17"/>
+    <mergeCell ref="A21"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="E15"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A14"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F23"/>
+    <mergeCell ref="F22"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A23"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2046,14 +2072,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>闭环单（闭环阶段 · 闭环方式由分析阶段继承）</t>
+          <t>闭环单（闭环阶段 · 闭环方式与单号由分析阶段继承）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>关联：主诉求单号    闭环方式由分析阶段继承,通过即进入验收</t>
+          <t>关联：主诉求单号    闭环方式与单号均由分析阶段继承</t>
         </is>
       </c>
     </row>
@@ -2081,8 +2107,16 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>闭环单号</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>(系统生成)</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
@@ -2318,8 +2352,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="B4:F4"/>
+  <mergeCells count="40">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="A17"/>
@@ -2332,6 +2365,7 @@
     <mergeCell ref="A19"/>
     <mergeCell ref="F14"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E18"/>
     <mergeCell ref="A15"/>
@@ -2357,6 +2391,7 @@
     <mergeCell ref="E15"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="A14"/>
+    <mergeCell ref="B4:C4"/>
     <mergeCell ref="F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
